--- a/H2coco/SR.xlsx
+++ b/H2coco/SR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69E2E3F0-B7BA-4742-B42A-3937761D0059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DE9A713-7656-2B4F-AFEA-43AF29220EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2200" windowWidth="28040" windowHeight="17180" xr2:uid="{CAD98384-3937-E94C-9B7F-ADEB78996059}"/>
+    <workbookView xWindow="3080" yWindow="2200" windowWidth="28040" windowHeight="17180" xr2:uid="{E994220F-3730-324F-A54A-5472628A13DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,20 +63,13 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -105,12 +98,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,35 +436,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B58FE5-9785-5546-83A2-51F86CA58709}">
-  <dimension ref="A1:E14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5261A86-402D-664A-A80E-8BD8501F01D3}">
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>46013</v>
       </c>
       <c r="B2" s="2">
@@ -481,216 +472,295 @@
       <c r="C2" s="2">
         <v>37164</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>8406.5</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>12693.56</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>46064</v>
+      <c r="A3" s="1">
+        <v>46093</v>
       </c>
       <c r="B3" s="2">
-        <v>5097</v>
+        <v>5089</v>
       </c>
       <c r="C3" s="2">
-        <v>37387</v>
-      </c>
-      <c r="D3" s="4">
+        <v>37379</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8663.14</v>
+      </c>
+      <c r="E3" s="3">
+        <v>12138.18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B4" s="2">
+        <v>5191</v>
+      </c>
+      <c r="C4" s="2">
+        <v>37813</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9438</v>
+      </c>
+      <c r="E4" s="3">
+        <v>13466.43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5197</v>
+      </c>
+      <c r="C5" s="2">
+        <v>37819</v>
+      </c>
+      <c r="D5" s="3">
+        <v>9503.2999999999993</v>
+      </c>
+      <c r="E5" s="3">
+        <v>13559.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5196</v>
+      </c>
+      <c r="C6" s="2">
+        <v>37818</v>
+      </c>
+      <c r="D6" s="3">
         <v>9600</v>
       </c>
-      <c r="E3" s="4">
-        <v>13529</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>46064</v>
-      </c>
-      <c r="B4" s="2">
-        <v>5099</v>
-      </c>
-      <c r="C4" s="2">
-        <v>37389</v>
-      </c>
-      <c r="D4" s="4">
-        <v>9569.1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>13485.45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>46093</v>
-      </c>
-      <c r="B5" s="2">
-        <v>5089</v>
-      </c>
-      <c r="C5" s="2">
-        <v>37379</v>
-      </c>
-      <c r="D5" s="4">
-        <v>8663.14</v>
-      </c>
-      <c r="E5" s="4">
-        <v>12138.18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>46093</v>
-      </c>
-      <c r="B6" s="2">
-        <v>5092</v>
-      </c>
-      <c r="C6" s="2">
-        <v>37382</v>
-      </c>
-      <c r="D6" s="4">
-        <v>9600</v>
-      </c>
-      <c r="E6" s="4">
-        <v>13450.84</v>
+      <c r="E6" s="3">
+        <v>13566.43</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>46093</v>
+      <c r="A7" s="1">
+        <v>46122</v>
       </c>
       <c r="B7" s="2">
-        <v>5198</v>
+        <v>5202</v>
       </c>
       <c r="C7" s="2">
-        <v>37820</v>
-      </c>
-      <c r="D7" s="4">
-        <v>7920</v>
-      </c>
-      <c r="E7" s="4">
-        <v>11096.94</v>
+        <v>37824</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9307.2000000000007</v>
+      </c>
+      <c r="E7" s="3">
+        <v>13152.65</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>46097</v>
+      <c r="A8" s="1">
+        <v>46122</v>
       </c>
       <c r="B8" s="2">
-        <v>5191</v>
+        <v>5283</v>
       </c>
       <c r="C8" s="2">
-        <v>37813</v>
-      </c>
-      <c r="D8" s="4">
-        <v>9438</v>
-      </c>
-      <c r="E8" s="4">
-        <v>13466.43</v>
+        <v>38069</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10010</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14145.83</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>46097</v>
+      <c r="A9" s="1">
+        <v>46129</v>
       </c>
       <c r="B9" s="2">
-        <v>5192</v>
+        <v>5384</v>
       </c>
       <c r="C9" s="2">
-        <v>37814</v>
-      </c>
-      <c r="D9" s="4">
-        <v>10020</v>
-      </c>
-      <c r="E9" s="4">
-        <v>14296.84</v>
+        <v>38232</v>
+      </c>
+      <c r="D9" s="3">
+        <v>9975</v>
+      </c>
+      <c r="E9" s="3">
+        <v>13834.52</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>46097</v>
+      <c r="A10" s="1">
+        <v>46129</v>
       </c>
       <c r="B10" s="2">
-        <v>5194</v>
+        <v>5385</v>
       </c>
       <c r="C10" s="2">
-        <v>37816</v>
-      </c>
-      <c r="D10" s="4">
-        <v>9182</v>
-      </c>
-      <c r="E10" s="4">
-        <v>13101.16</v>
+        <v>38233</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9830</v>
+      </c>
+      <c r="E10" s="3">
+        <v>13633.43</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>46097</v>
+      <c r="A11" s="1">
+        <v>46129</v>
       </c>
       <c r="B11" s="2">
-        <v>5195</v>
+        <v>5386</v>
       </c>
       <c r="C11" s="2">
-        <v>37817</v>
-      </c>
-      <c r="D11" s="4">
-        <v>10008</v>
-      </c>
-      <c r="E11" s="4">
-        <v>14279.72</v>
+        <v>38234</v>
+      </c>
+      <c r="D11" s="3">
+        <v>9825</v>
+      </c>
+      <c r="E11" s="3">
+        <v>13626.49</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>46097</v>
+      <c r="A12" s="1">
+        <v>46129</v>
       </c>
       <c r="B12" s="2">
-        <v>5197</v>
+        <v>5387</v>
       </c>
       <c r="C12" s="2">
-        <v>37819</v>
-      </c>
-      <c r="D12" s="4">
-        <v>9503.2999999999993</v>
-      </c>
-      <c r="E12" s="4">
-        <v>13559.6</v>
+        <v>38236</v>
+      </c>
+      <c r="D12" s="3">
+        <v>10050</v>
+      </c>
+      <c r="E12" s="3">
+        <v>13792.92</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>46097</v>
+      <c r="A13" s="1">
+        <v>46129</v>
       </c>
       <c r="B13" s="2">
-        <v>5200</v>
+        <v>5454</v>
       </c>
       <c r="C13" s="2">
-        <v>37822</v>
-      </c>
-      <c r="D13" s="4">
-        <v>10040</v>
-      </c>
-      <c r="E13" s="4">
-        <v>14325.38</v>
+        <v>37055</v>
+      </c>
+      <c r="D13" s="3">
+        <v>11550</v>
+      </c>
+      <c r="E13" s="3">
+        <v>16018.93</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>46097</v>
+      <c r="A14" s="1">
+        <v>46129</v>
       </c>
       <c r="B14" s="2">
-        <v>5201</v>
+        <v>5455</v>
       </c>
       <c r="C14" s="2">
-        <v>37923</v>
-      </c>
-      <c r="D14" s="4">
-        <v>9307.2000000000007</v>
-      </c>
-      <c r="E14" s="4">
-        <v>13279.8</v>
-      </c>
+        <v>37048</v>
+      </c>
+      <c r="D14" s="3">
+        <v>11550</v>
+      </c>
+      <c r="E14" s="3">
+        <v>16018.93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B15" s="2">
+        <v>5456</v>
+      </c>
+      <c r="C15" s="2">
+        <v>37051</v>
+      </c>
+      <c r="D15" s="3">
+        <v>11550</v>
+      </c>
+      <c r="E15" s="3">
+        <v>16018.93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5457</v>
+      </c>
+      <c r="C16" s="2">
+        <v>37052</v>
+      </c>
+      <c r="D16" s="3">
+        <v>11550</v>
+      </c>
+      <c r="E16" s="3">
+        <v>16018.93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/H2coco/SR.xlsx
+++ b/H2coco/SR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DE9A713-7656-2B4F-AFEA-43AF29220EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CBFBBEC-4668-C948-90F1-225EE7656AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2200" windowWidth="28040" windowHeight="17180" xr2:uid="{E994220F-3730-324F-A54A-5472628A13DB}"/>
+    <workbookView xWindow="17100" yWindow="800" windowWidth="17100" windowHeight="21440" xr2:uid="{43021A36-C419-9443-8BE7-A6A690B376F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -436,16 +436,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5261A86-402D-664A-A80E-8BD8501F01D3}">
-  <dimension ref="A1:E25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA6EFF0-E7D3-E546-9089-1FFED6EC9DE8}">
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -462,305 +457,313 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>46013</v>
+        <v>46129</v>
       </c>
       <c r="B2" s="2">
-        <v>5013</v>
+        <v>5386</v>
       </c>
       <c r="C2" s="2">
-        <v>37164</v>
+        <v>38234</v>
       </c>
       <c r="D2" s="3">
-        <v>8406.5</v>
+        <v>9825</v>
       </c>
       <c r="E2" s="3">
-        <v>12693.56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13626.49</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>46093</v>
+        <v>46147</v>
       </c>
       <c r="B3" s="2">
-        <v>5089</v>
+        <v>5465</v>
       </c>
       <c r="C3" s="2">
-        <v>37379</v>
+        <v>38467</v>
       </c>
       <c r="D3" s="3">
-        <v>8663.14</v>
+        <v>9600</v>
       </c>
       <c r="E3" s="3">
-        <v>12138.18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13394.1</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>46097</v>
+        <v>46147</v>
       </c>
       <c r="B4" s="2">
-        <v>5191</v>
+        <v>5464</v>
       </c>
       <c r="C4" s="2">
-        <v>37813</v>
+        <v>38468</v>
       </c>
       <c r="D4" s="3">
-        <v>9438</v>
+        <v>8889.5</v>
       </c>
       <c r="E4" s="3">
-        <v>13466.43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>12402.81</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>46097</v>
+        <v>46147</v>
       </c>
       <c r="B5" s="2">
-        <v>5197</v>
+        <v>5463</v>
       </c>
       <c r="C5" s="2">
-        <v>37819</v>
+        <v>38469</v>
       </c>
       <c r="D5" s="3">
-        <v>9503.2999999999993</v>
+        <v>9840</v>
       </c>
       <c r="E5" s="3">
-        <v>13559.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13728.96</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>46122</v>
+        <v>46147</v>
       </c>
       <c r="B6" s="2">
-        <v>5196</v>
+        <v>5462</v>
       </c>
       <c r="C6" s="2">
-        <v>37818</v>
+        <v>38470</v>
       </c>
       <c r="D6" s="3">
+        <v>9642</v>
+      </c>
+      <c r="E6" s="3">
+        <v>13452.71</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5460</v>
+      </c>
+      <c r="C7" s="2">
+        <v>38472</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7920</v>
+      </c>
+      <c r="E7" s="3">
+        <v>11050.14</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5459</v>
+      </c>
+      <c r="C8" s="2">
+        <v>38473</v>
+      </c>
+      <c r="D8" s="3">
         <v>9600</v>
       </c>
-      <c r="E6" s="3">
-        <v>13566.43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>46122</v>
-      </c>
-      <c r="B7" s="2">
-        <v>5202</v>
-      </c>
-      <c r="C7" s="2">
-        <v>37824</v>
-      </c>
-      <c r="D7" s="3">
-        <v>9307.2000000000007</v>
-      </c>
-      <c r="E7" s="3">
-        <v>13152.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>46122</v>
-      </c>
-      <c r="B8" s="2">
-        <v>5283</v>
-      </c>
-      <c r="C8" s="2">
-        <v>38069</v>
-      </c>
-      <c r="D8" s="3">
-        <v>10010</v>
-      </c>
       <c r="E8" s="3">
-        <v>14145.83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13394.11</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>46129</v>
+        <v>46147</v>
       </c>
       <c r="B9" s="2">
-        <v>5384</v>
+        <v>5458</v>
       </c>
       <c r="C9" s="2">
-        <v>38232</v>
+        <v>38474</v>
       </c>
       <c r="D9" s="3">
+        <v>9413.75</v>
+      </c>
+      <c r="E9" s="3">
+        <v>13134.25</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5587</v>
+      </c>
+      <c r="C10" s="2">
+        <v>38837</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9443</v>
+      </c>
+      <c r="E10" s="3">
+        <v>13154.57</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B11" s="2">
+        <v>5591</v>
+      </c>
+      <c r="C11" s="2">
+        <v>38838</v>
+      </c>
+      <c r="D11" s="3">
         <v>9975</v>
       </c>
-      <c r="E9" s="3">
-        <v>13834.52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>46129</v>
-      </c>
-      <c r="B10" s="2">
-        <v>5385</v>
-      </c>
-      <c r="C10" s="2">
-        <v>38233</v>
-      </c>
-      <c r="D10" s="3">
-        <v>9830</v>
-      </c>
-      <c r="E10" s="3">
-        <v>13633.43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>46129</v>
-      </c>
-      <c r="B11" s="2">
-        <v>5386</v>
-      </c>
-      <c r="C11" s="2">
-        <v>38234</v>
-      </c>
-      <c r="D11" s="3">
-        <v>9825</v>
-      </c>
       <c r="E11" s="3">
-        <v>13626.49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13895.68</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>46129</v>
+        <v>46171</v>
       </c>
       <c r="B12" s="2">
-        <v>5387</v>
+        <v>5592</v>
       </c>
       <c r="C12" s="2">
-        <v>38236</v>
+        <v>38839</v>
       </c>
       <c r="D12" s="3">
-        <v>10050</v>
+        <v>9618.75</v>
       </c>
       <c r="E12" s="3">
-        <v>13792.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13399.41</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>46129</v>
+        <v>46171</v>
       </c>
       <c r="B13" s="2">
-        <v>5454</v>
+        <v>5593</v>
       </c>
       <c r="C13" s="2">
-        <v>37055</v>
+        <v>38840</v>
       </c>
       <c r="D13" s="3">
-        <v>11550</v>
+        <v>10055</v>
       </c>
       <c r="E13" s="3">
-        <v>16018.93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>14007.12</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>46129</v>
+        <v>46171</v>
       </c>
       <c r="B14" s="2">
-        <v>5455</v>
+        <v>5594</v>
       </c>
       <c r="C14" s="2">
-        <v>37048</v>
+        <v>38841</v>
       </c>
       <c r="D14" s="3">
-        <v>11550</v>
+        <v>9364</v>
       </c>
       <c r="E14" s="3">
-        <v>16018.93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13044.53</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>46129</v>
+        <v>46171</v>
       </c>
       <c r="B15" s="2">
-        <v>5456</v>
+        <v>5596</v>
       </c>
       <c r="C15" s="2">
-        <v>37051</v>
+        <v>38876</v>
       </c>
       <c r="D15" s="3">
-        <v>11550</v>
+        <v>10275</v>
       </c>
       <c r="E15" s="3">
-        <v>16018.93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>46129</v>
-      </c>
-      <c r="B16" s="2">
-        <v>5457</v>
-      </c>
-      <c r="C16" s="2">
-        <v>37052</v>
-      </c>
-      <c r="D16" s="3">
-        <v>11550</v>
-      </c>
-      <c r="E16" s="3">
-        <v>16018.93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+        <v>14313.6</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
